--- a/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,110 @@
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>080104</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I-442135</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>080104</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-13.5568768</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-71.9154734</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>080104</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-442133</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>080104</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-13.5511259</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-71.9121334</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>080104</t>
         </is>

--- a/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>080104</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-391154</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>080104</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-13.5425766</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>080104</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>080104</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-331375</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>080104</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-13.5491767</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>080104</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>080104</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-33246</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>080104</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-13.5468584</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>080104</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>080104</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-33303</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>080104</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-13.5435398</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>080104</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>080104</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-442135</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>080104</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-13.5568768</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>080104</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>080104</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-442133</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>080104</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-13.5511259</t>
@@ -784,11 +754,6 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>080104</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/CUSCO-CUSCO-SAN_JERONIMO.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-391154</t>
+          <t>I-442135</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.5425766</t>
+          <t>-13.5568768</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-71.8982485</t>
+          <t>-71.9154734</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida de la Cultura / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,17 +533,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-331375</t>
+          <t>I-442133</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-13.5491767</t>
+          <t>-13.5511259</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-71.9057539</t>
+          <t>-71.9121334</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-33246</t>
+          <t>I-391154</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-13.5468584</t>
+          <t>-13.5425766</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-71.8949947</t>
+          <t>-71.8982485</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida de la Cultura / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-33303</t>
+          <t>I-390693</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-13.5435398</t>
+          <t>-13.5452699</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-71.9044622</t>
+          <t>-71.9066143</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-442135</t>
+          <t>I-390682</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-13.5568768</t>
+          <t>-13.5451736</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-71.9154734</t>
+          <t>-71.9047994</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-442133</t>
+          <t>I-390662</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-13.5511259</t>
+          <t>-13.5488467</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-71.9121334</t>
+          <t>-71.9000707</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-17354</t>
+          <t>I-390383</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-13.54454</t>
+          <t>-13.539524</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-71.8873237</t>
+          <t>-71.8798368</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-33416</t>
+          <t>I-390245</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-13.5423756</t>
+          <t>-13.5469167</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-71.8866376</t>
+          <t>-71.8789731</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-232392</t>
+          <t>I-389214</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-13.5417895</t>
+          <t>-13.5313509</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-71.8949064</t>
+          <t>-71.8977472</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-390693</t>
+          <t>I-389174</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-13.5452699</t>
+          <t>-13.5271921</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-71.9066143</t>
+          <t>-71.896424</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-332325</t>
+          <t>I-361625</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-13.5493437</t>
+          <t>-13.5462634</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-71.9053382</t>
+          <t>-71.8770275</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-331345</t>
+          <t>I-33416</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-13.5496762</t>
+          <t>-13.5423756</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-71.8969779</t>
+          <t>-71.8866376</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1050,27 +1050,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-197369</t>
+          <t>I-33303</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-13.5489504</t>
+          <t>-13.5435398</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-71.8939775</t>
+          <t>-71.9044622</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1097,27 +1097,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-389214</t>
+          <t>I-33246</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-13.5313509</t>
+          <t>-13.5468584</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-71.8977472</t>
+          <t>-71.8949947</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-32724</t>
+          <t>I-33245</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-13.5480138</t>
+          <t>-13.5449651</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-71.8772876</t>
+          <t>-71.8884318</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-361625</t>
+          <t>I-332338</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-13.5462634</t>
+          <t>-13.5480852</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-71.8770275</t>
+          <t>-71.907822</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-390682</t>
+          <t>I-332325</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-13.5451736</t>
+          <t>-13.5493437</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-71.9047994</t>
+          <t>-71.9053382</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,27 +1285,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-390662</t>
+          <t>I-331375</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-13.5488467</t>
+          <t>-13.5491767</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-71.9000707</t>
+          <t>-71.9057539</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-17341</t>
+          <t>I-331345</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-13.5420532</t>
+          <t>-13.5496762</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-71.8852402</t>
+          <t>-71.8969779</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-390383</t>
+          <t>I-32724</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-13.539524</t>
+          <t>-13.5480138</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-71.8798368</t>
+          <t>-71.8772876</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-389174</t>
+          <t>I-232392</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-13.5271921</t>
+          <t>-13.5417895</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-71.896424</t>
+          <t>-71.8949064</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-332338</t>
+          <t>I-197369</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-13.5480852</t>
+          <t>-13.5489504</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-71.907822</t>
+          <t>-71.8939775</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-390245</t>
+          <t>I-17363</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-13.5469167</t>
+          <t>-13.5433166</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-71.8789731</t>
+          <t>-71.8895824</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-17363</t>
+          <t>I-17354</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-13.5433166</t>
+          <t>-13.54454</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-71.8895824</t>
+          <t>-71.8873237</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1614,17 +1614,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-33245</t>
+          <t>I-17341</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-13.5449651</t>
+          <t>-13.5420532</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-71.8884318</t>
+          <t>-71.8852402</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
